--- a/tools/importer/reports/import-atelier.report.xlsx
+++ b/tools/importer/reports/import-atelier.report.xlsx
@@ -73,7 +73,7 @@
     <t>atelier</t>
   </si>
   <si>
-    <t>2026-07-17T13:35:58.688Z</t>
+    <t>2026-07-18T08:06:23.471Z</t>
   </si>
   <si>
     <t>The Atelier — Fréscopa</t>

--- a/tools/importer/reports/import-atelier.report.xlsx
+++ b/tools/importer/reports/import-atelier.report.xlsx
@@ -73,7 +73,7 @@
     <t>atelier</t>
   </si>
   <si>
-    <t>2026-07-18T08:06:23.471Z</t>
+    <t>2026-07-18T08:12:40.058Z</t>
   </si>
   <si>
     <t>The Atelier — Fréscopa</t>
